--- a/EX1/CPa results/CPa_for_LApredict_test_data.xlsx
+++ b/EX1/CPa results/CPa_for_LApredict_test_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CP_res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CPa results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FD80026-1334-4B79-AEEE-3341FA0A04F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB1E337-D855-44E0-A1D4-3079DB53408A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18040" yWindow="3010" windowWidth="24910" windowHeight="14110" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OP_0.05" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="20">
   <si>
     <t>Total correct made 
 by LApredict</t>
@@ -82,6 +82,24 @@
   <si>
     <t>Recall</t>
   </si>
+  <si>
+    <t>LApredict with Openstack makes 3707 correct predictions; 3506 clean and 201 fault-prone</t>
+  </si>
+  <si>
+    <t>LApredict with QT makes 4088 correct predictions; 4063 clean and 25 fault-prone</t>
+  </si>
+  <si>
+    <t>Precision_clean</t>
+  </si>
+  <si>
+    <t>recall_clean</t>
+  </si>
+  <si>
+    <t>Precision faulty</t>
+  </si>
+  <si>
+    <t>recall_faulty</t>
+  </si>
 </sst>
 </file>
 
@@ -90,7 +108,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -140,6 +158,19 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -196,7 +227,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -227,6 +258,13 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -355,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="2"/>
@@ -363,10 +401,11 @@
     <col min="7" max="7" width="13.44140625" style="1" customWidth="1"/>
     <col min="8" max="12" width="12.6640625" style="1"/>
     <col min="13" max="13" width="7.5546875" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="12.6640625" style="1"/>
+    <col min="14" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -410,8 +449,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3707</v>
       </c>
@@ -457,8 +508,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.46830321014297277</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.91554599246906943</v>
+      </c>
+      <c r="R2">
+        <f>J2/3506</f>
+        <v>0.4854535082715345</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="U2">
+        <f>I2/201</f>
+        <v>0.1691542288557214</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3707</v>
       </c>
@@ -504,8 +571,24 @@
         <f t="shared" si="1"/>
         <v>0.47504720798489347</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.91322751322751328</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/3506</f>
+        <v>0.49229891614375354</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/201</f>
+        <v>0.17412935323383086</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3707</v>
       </c>
@@ -551,8 +634,24 @@
         <f t="shared" si="1"/>
         <v>0.42163474507688159</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.91626794258373201</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.43696520250998289</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.79487179487179482</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.15422885572139303</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3707</v>
       </c>
@@ -598,8 +697,24 @@
         <f t="shared" si="1"/>
         <v>0.40248179120582683</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.9183929692404269</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.41728465487735311</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.78378378378378377</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.14427860696517414</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3707</v>
       </c>
@@ -645,8 +760,24 @@
         <f t="shared" si="1"/>
         <v>0.41165362827083896</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.91605392156862742</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.42641186537364517</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.79487179487179482</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.15422885572139303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3707</v>
       </c>
@@ -692,8 +823,24 @@
         <f t="shared" si="1"/>
         <v>0.45643377394119233</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.91455347298787215</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.47318881916714206</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.16417910447761194</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3707</v>
       </c>
@@ -739,8 +886,24 @@
         <f t="shared" si="1"/>
         <v>0.44861073644456434</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.91577765300393033</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.46520250998288648</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.15920398009950248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3707</v>
       </c>
@@ -786,8 +949,24 @@
         <f t="shared" si="1"/>
         <v>0.43512274076072294</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.91546033584250142</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.4509412435824301</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.8</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.15920398009950248</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3707</v>
       </c>
@@ -826,15 +1005,31 @@
       </c>
       <c r="M10"/>
       <c r="N10">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.91161087866108792</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.47019152953871057</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.91390374331550805</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.48745008556759839</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.1691542288557214</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3707</v>
       </c>
@@ -873,15 +1068,31 @@
       </c>
       <c r="M11"/>
       <c r="N11">
+        <f t="shared" si="6"/>
+        <v>0.91141219385096406</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="7"/>
+        <v>0.47181008902077154</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.91141219385096406</v>
-      </c>
-      <c r="O11">
+        <v>0.91417910447761197</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.47181008902077154</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.48916143753565317</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.79069767441860461</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.1691542288557214</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -920,6 +1131,42 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.44612894523873753</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.91533626487167941</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.46243582430119795</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.79659284935518615</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.1616915422885572</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>1771.3999999999999</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>40.799999999999997</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="15" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="16" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -934,14 +1181,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:U61"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -985,8 +1233,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3707</v>
       </c>
@@ -1032,8 +1292,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.65147019152953867</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.89613343442001514</v>
+      </c>
+      <c r="R2">
+        <f>J2/3506</f>
+        <v>0.67427267541357672</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="U2">
+        <f>I2/201</f>
+        <v>0.2537313432835821</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3707</v>
       </c>
@@ -1079,8 +1355,24 @@
         <f t="shared" si="1"/>
         <v>0.68680874022120308</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.89251164457183807</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/3506</f>
+        <v>0.71049629207073584</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.70512820512820518</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/201</f>
+        <v>0.27363184079601988</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3707</v>
       </c>
@@ -1126,8 +1418,24 @@
         <f t="shared" si="1"/>
         <v>0.65605611006204478</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.89511278195488719</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.67912150598973187</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.2537313432835821</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3707</v>
       </c>
@@ -1173,8 +1481,24 @@
         <f t="shared" si="1"/>
         <v>0.65632586997572162</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.89515219842164595</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.67940673131774099</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.2537313432835821</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3707</v>
       </c>
@@ -1220,8 +1544,24 @@
         <f t="shared" si="1"/>
         <v>0.64310763420555705</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.89911436272622258</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.66600114090131202</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.7</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.24378109452736318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3707</v>
       </c>
@@ -1267,8 +1607,24 @@
         <f t="shared" si="1"/>
         <v>0.65254923118424601</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.89629068887206664</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.6754135767256132</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.2537313432835821</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3707</v>
       </c>
@@ -1314,8 +1670,24 @@
         <f t="shared" si="1"/>
         <v>0.69490153763150797</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.89266737513283745</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.71876782658300054</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.70886075949367089</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.27860696517412936</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3707</v>
       </c>
@@ -1361,8 +1733,24 @@
         <f t="shared" si="1"/>
         <v>0.68006474237928249</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.89420289855072466</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.70393610952652597</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.70666666666666667</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.26368159203980102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3707</v>
       </c>
@@ -1401,15 +1789,31 @@
       </c>
       <c r="M10"/>
       <c r="N10">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.89143279172821266</v>
       </c>
       <c r="O10">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.65120043161586183</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.89647326507394764</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.67427267541357672</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.70422535211267601</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.24875621890547264</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3707</v>
       </c>
@@ -1448,15 +1852,31 @@
       </c>
       <c r="M11"/>
       <c r="N11">
+        <f t="shared" si="6"/>
+        <v>0.88803088803088803</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="7"/>
+        <v>0.68249258160237392</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.88803088803088803</v>
-      </c>
-      <c r="O11">
+        <v>0.8929343907714492</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.68249258160237392</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.70650313747860805</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.70666666666666667</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.26368159203980102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1496,8 +1916,39 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.66549770704073363</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.89505930404956335</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.68881916714204228</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.70648809834012194</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.25870646766169159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>2698.3</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>73.599999999999994</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -1505,7 +1956,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1513,7 +1964,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1883,14 +2334,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -1934,8 +2386,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>3707</v>
       </c>
@@ -1982,8 +2446,24 @@
         <v>0.83868357162125706</v>
       </c>
       <c r="P2" s="12"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.86901327178303522</v>
+      </c>
+      <c r="R2">
+        <f>J2/3506</f>
+        <v>0.8590986879634912</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.66896551724137931</v>
+      </c>
+      <c r="U2">
+        <f>I2/201</f>
+        <v>0.48258706467661694</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3707</v>
       </c>
@@ -2029,8 +2509,24 @@
         <f t="shared" ref="O3:O9" si="1">G3/A3</f>
         <v>0.80496358241165367</v>
       </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.87583081570996979</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/3506</f>
+        <v>0.82686822589845976</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.68</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/201</f>
+        <v>0.4228855721393035</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3707</v>
       </c>
@@ -2076,8 +2572,24 @@
         <f t="shared" si="1"/>
         <v>0.80091718370650122</v>
       </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.87587253414264032</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.82316029663434109</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.67479674796747968</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.41293532338308458</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3707</v>
       </c>
@@ -2123,8 +2635,24 @@
         <f t="shared" si="1"/>
         <v>0.8322093336930132</v>
       </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.86969168121000584</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.85282373074729034</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.66433566433566438</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.47263681592039802</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>3707</v>
       </c>
@@ -2170,8 +2698,24 @@
         <f t="shared" si="1"/>
         <v>0.81683301861343405</v>
       </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.87306777645659928</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.83770678836280665</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.68939393939393945</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.45273631840796019</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3707</v>
       </c>
@@ -2217,8 +2761,24 @@
         <f t="shared" si="1"/>
         <v>0.8014567035338549</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.87594783136184406</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.82373074729035933</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.67479674796747968</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.41293532338308458</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>3707</v>
       </c>
@@ -2264,8 +2824,24 @@
         <f t="shared" si="1"/>
         <v>0.83787429188022655</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.86889979786312443</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.85824301197946373</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.66896551724137931</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.48258706467661694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>3707</v>
       </c>
@@ -2311,8 +2887,24 @@
         <f t="shared" si="1"/>
         <v>0.81764229835446456</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.87318087318087323</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.83856246434683401</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.68939393939393945</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.45273631840796019</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>3707</v>
       </c>
@@ -2361,8 +2953,24 @@
       <c r="P10" s="1">
         <v>0.83787429188022655</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.86889979786312443</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.85824301197946373</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.66896551724137931</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.48258706467661694</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>3707</v>
       </c>
@@ -2408,8 +3016,24 @@
         <f>G11/A11</f>
         <v>0.83652549231184248</v>
       </c>
-    </row>
-    <row r="12" spans="1:16" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q11">
+        <f t="shared" si="2"/>
+        <v>0.86925079548741679</v>
+      </c>
+      <c r="R11">
+        <f t="shared" si="3"/>
+        <v>0.85710211066742725</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.47761194029850745</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2449,6 +3073,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.82249797680064751</v>
       </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="6">AVERAGE(Q2:Q11)</f>
+        <v>0.87196551750586337</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="6"/>
+        <v>0.84355390758699378</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="7">AVERAGE(T2:T11)</f>
+        <v>0.67462802574493075</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="7"/>
+        <v>0.45522388059701491</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>3392</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>135.69999999999999</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -2462,13 +3117,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U15"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="12.6640625" style="1"/>
+    <col min="1" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -2512,8 +3168,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>4088</v>
       </c>
@@ -2558,8 +3226,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.65704500978473579</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.90404040404040409</v>
+      </c>
+      <c r="R2">
+        <f>J2/4063</f>
+        <v>0.66084174255476247</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U2">
+        <f>I2/25</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>4088</v>
       </c>
@@ -2604,8 +3288,24 @@
         <f t="shared" si="1"/>
         <v>0.59124266144814086</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.90758827948910592</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/4063</f>
+        <v>0.59463450652227423</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.25</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/25</f>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4088</v>
       </c>
@@ -2650,8 +3350,24 @@
         <f t="shared" si="1"/>
         <v>0.59344422700587085</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.90789966304754777</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.59684961850849128</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4088</v>
       </c>
@@ -2696,8 +3412,24 @@
         <f t="shared" si="1"/>
         <v>0.49706457925636005</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.91983695652173914</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.49987693822298795</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4088</v>
       </c>
@@ -2742,8 +3474,24 @@
         <f t="shared" si="1"/>
         <v>0.66364970645792565</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.90309690309690305</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.66748707851341371</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4088</v>
       </c>
@@ -2788,8 +3536,24 @@
         <f t="shared" si="1"/>
         <v>0.5689823874755382</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.91140729125833009</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.57223726310607925</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4088</v>
       </c>
@@ -2834,8 +3598,24 @@
         <f t="shared" si="1"/>
         <v>0.64848336594911937</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.90381991814461116</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.65222741816391827</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4088</v>
       </c>
@@ -2880,8 +3660,24 @@
         <f t="shared" si="1"/>
         <v>0.57999021526418781</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.90943975441289338</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.5833128230371647</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>4088</v>
       </c>
@@ -2919,15 +3715,31 @@
         <v>3</v>
       </c>
       <c r="N10" s="2">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.91044192412983971</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.56947162426614484</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.91147669408538978</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.57272951021412755</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>4088</v>
       </c>
@@ -2965,15 +3777,31 @@
         <v>3</v>
       </c>
       <c r="N11" s="2">
+        <f t="shared" si="6"/>
+        <v>0.90393317090149672</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="7"/>
+        <v>0.63527397260273977</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.90393317090149672</v>
-      </c>
-      <c r="O11" s="2">
+        <v>0.9048448936911816</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.63527397260273977</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.63893674624661578</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3012,6 +3840,42 @@
       <c r="O12" s="9">
         <f>AVERAGE(O2:O11)</f>
         <v>0.60046477495107631</v>
+      </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.90834507577881074</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.60391336450898359</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.2583333333333333</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>3.9999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>2702.5</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>3.9</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
+    </row>
+    <row r="15" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3026,14 +3890,15 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:U13"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="12.6640625" style="1"/>
+    <col min="2" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3077,8 +3942,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>4088</v>
       </c>
@@ -3124,8 +4001,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.89995107632093929</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.87535748331744523</v>
+      </c>
+      <c r="R2">
+        <f>J2/4063</f>
+        <v>0.90401181393059316</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U2">
+        <f>I2/25</f>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>4088</v>
       </c>
@@ -3171,8 +4064,24 @@
         <f t="shared" si="1"/>
         <v>0.85053816046966735</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.88304093567251463</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/4063</f>
+        <v>0.85478710312576911</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.5</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/25</f>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4088</v>
       </c>
@@ -3218,8 +4127,24 @@
         <f>G4/A4</f>
         <v>0.89603718199608606</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.87676816111244305</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.90007383706620725</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4088</v>
       </c>
@@ -3265,8 +4190,24 @@
         <f t="shared" si="1"/>
         <v>0.82681017612524466</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.88702049395691018</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.83091311838542947</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4088</v>
       </c>
@@ -3312,8 +4253,24 @@
         <f t="shared" si="1"/>
         <v>0.8595890410958904</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.88080301129234628</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.8638936746246616</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4088</v>
       </c>
@@ -3359,8 +4316,24 @@
         <f>G7/A7</f>
         <v>0.86986301369863017</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.87983151635282453</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.87398474033965046</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4088</v>
       </c>
@@ -3406,8 +4379,24 @@
         <f t="shared" si="1"/>
         <v>0.93175146771037187</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.86905850091407677</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>0.93600787595372881</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4088</v>
       </c>
@@ -3453,8 +4442,24 @@
         <f t="shared" si="1"/>
         <v>0.82681017612524466</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.88702049395691018</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.83091311838542947</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>4088</v>
       </c>
@@ -3493,15 +4498,31 @@
       </c>
       <c r="M10"/>
       <c r="N10" s="10">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.88203957382039577</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.85053816046966735</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.88281647178444334</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.85478710312576911</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>4088</v>
       </c>
@@ -3540,15 +4561,31 @@
       </c>
       <c r="M11"/>
       <c r="N11" s="10">
+        <f t="shared" si="6"/>
+        <v>0.87623167507810618</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="7"/>
+        <v>0.89187866927592951</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.87623167507810618</v>
-      </c>
-      <c r="O11" s="2">
+        <v>0.87710843373493974</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.89187866927592951</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.89588973664779714</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -3588,6 +4625,37 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.87037671232876712</v>
       </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.87988255020948558</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.87452621215850357</v>
+      </c>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.51363636363636367</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.19600000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>4039.2999999999997</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>9.5</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
   </sheetData>
   <pageMargins left="0.78750000000000009" right="0.78750000000000009" top="1.0249999999999997" bottom="1.0249999999999997" header="0.78750000000000009" footer="0.78750000000000009"/>
@@ -3601,17 +4669,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="1" customWidth="1"/>
     <col min="2" max="12" width="12.6640625" style="1"/>
     <col min="13" max="13" width="16.77734375" style="1" customWidth="1"/>
     <col min="15" max="15" width="12.6640625" style="2"/>
-    <col min="16" max="16384" width="12.6640625" style="1"/>
+    <col min="16" max="16" width="12.6640625" style="1"/>
+    <col min="22" max="16384" width="12.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="62.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="62.4" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
@@ -3655,8 +4724,20 @@
       <c r="O1" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>4088</v>
       </c>
@@ -3702,8 +4783,24 @@
         <f t="shared" ref="O2:O9" si="1">G2/A2</f>
         <v>0.99535225048923681</v>
       </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q2">
+        <f>J2/(J2+K2)</f>
+        <v>0.85893084429359357</v>
+      </c>
+      <c r="R2">
+        <f>J2/4063</f>
+        <v>0.99655427024366228</v>
+      </c>
+      <c r="T2">
+        <f>I2/(I2+L2)</f>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="U2">
+        <f>I2/25</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>4088</v>
       </c>
@@ -3749,8 +4846,24 @@
         <f t="shared" si="1"/>
         <v>0.98899217221135027</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q3">
+        <f t="shared" ref="Q3:Q11" si="2">J3/(J3+K3)</f>
+        <v>0.86068376068376073</v>
+      </c>
+      <c r="R3">
+        <f t="shared" ref="R3:R11" si="3">J3/4063</f>
+        <v>0.9913856756091558</v>
+      </c>
+      <c r="T3">
+        <f t="shared" ref="T3:T11" si="4">I3/(I3+L3)</f>
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="U3">
+        <f t="shared" ref="U3:U11" si="5">I3/25</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>4088</v>
       </c>
@@ -3796,8 +4909,24 @@
         <f t="shared" si="1"/>
         <v>0.98899217221135027</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q4">
+        <f t="shared" si="2"/>
+        <v>0.86068376068376073</v>
+      </c>
+      <c r="R4">
+        <f t="shared" si="3"/>
+        <v>0.9913856756091558</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="4"/>
+        <v>0.57692307692307687</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="5"/>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>4088</v>
       </c>
@@ -3843,8 +4972,24 @@
         <f t="shared" si="1"/>
         <v>0.97847358121330719</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q5">
+        <f t="shared" si="2"/>
+        <v>0.86136903476570936</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="3"/>
+        <v>0.98178685700221513</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="5"/>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4088</v>
       </c>
@@ -3890,8 +5035,24 @@
         <f t="shared" si="1"/>
         <v>0.9821428571428571</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q6">
+        <f t="shared" si="2"/>
+        <v>0.86120077469335055</v>
+      </c>
+      <c r="R6">
+        <f t="shared" si="3"/>
+        <v>0.98498646320452865</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="4"/>
+        <v>0.56521739130434778</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>4088</v>
       </c>
@@ -3937,8 +5098,24 @@
         <f t="shared" si="1"/>
         <v>0.97847358121330719</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q7">
+        <f t="shared" si="2"/>
+        <v>0.8615550755939525</v>
+      </c>
+      <c r="R7">
+        <f t="shared" si="3"/>
+        <v>0.98178685700221513</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="4"/>
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="5"/>
+        <v>0.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>4088</v>
       </c>
@@ -3984,8 +5161,24 @@
         <f>G8/A8</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q8">
+        <f t="shared" si="2"/>
+        <v>0.85844073526304665</v>
+      </c>
+      <c r="R8">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="4"/>
+        <v>0.5</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>4088</v>
       </c>
@@ -4031,8 +5224,24 @@
         <f t="shared" si="1"/>
         <v>0.97676125244618395</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q9">
+        <f t="shared" si="2"/>
+        <v>0.86215104955637312</v>
+      </c>
+      <c r="R9">
+        <f t="shared" si="3"/>
+        <v>0.98055623923209456</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="4"/>
+        <v>0.47368421052631576</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="5"/>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>4088</v>
       </c>
@@ -4071,15 +5280,31 @@
       </c>
       <c r="M10"/>
       <c r="N10" s="2">
-        <f t="shared" ref="N10:N11" si="2">G10/E10</f>
+        <f t="shared" ref="N10:N11" si="6">G10/E10</f>
         <v>0.8597951344430218</v>
       </c>
       <c r="O10" s="2">
-        <f t="shared" ref="O10:O11" si="3">G10/A10</f>
+        <f t="shared" ref="O10:O11" si="7">G10/A10</f>
         <v>0.98556751467710368</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="Q10">
+        <f t="shared" si="2"/>
+        <v>0.86143286143286146</v>
+      </c>
+      <c r="R10">
+        <f t="shared" si="3"/>
+        <v>0.98843219296086637</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="4"/>
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="5"/>
+        <v>0.52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>4088</v>
       </c>
@@ -4118,15 +5343,31 @@
       </c>
       <c r="M11"/>
       <c r="N11" s="2">
+        <f t="shared" si="6"/>
+        <v>0.85786694825765575</v>
+      </c>
+      <c r="O11" s="2">
+        <f t="shared" si="7"/>
+        <v>0.99363992172211346</v>
+      </c>
+      <c r="Q11">
         <f t="shared" si="2"/>
-        <v>0.85786694825765575</v>
-      </c>
-      <c r="O11" s="2">
+        <v>0.85954101147471318</v>
+      </c>
+      <c r="R11">
         <f t="shared" si="3"/>
-        <v>0.99363992172211346</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
+        <v>0.9955697760275658</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="4"/>
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="5"/>
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" s="6" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="E12" s="7">
         <f>AVERAGE(E2:E11)</f>
         <v>4697.6000000000004</v>
@@ -4161,6 +5402,38 @@
         <f>AVERAGE(O2:O11)</f>
         <v>0.9868395303326809</v>
       </c>
+      <c r="Q12" s="17">
+        <f t="shared" ref="Q12:R12" si="8">AVERAGE(Q2:Q11)</f>
+        <v>0.86059889084411212</v>
+      </c>
+      <c r="R12" s="17">
+        <f t="shared" si="8"/>
+        <v>0.98924440068914588</v>
+      </c>
+      <c r="S12"/>
+      <c r="T12" s="17">
+        <f t="shared" ref="T12:U12" si="9">AVERAGE(T2:T11)</f>
+        <v>0.54743009725748615</v>
+      </c>
+      <c r="U12" s="17">
+        <f t="shared" si="9"/>
+        <v>0.59600000000000009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="J13" s="15">
+        <f>J12+K12</f>
+        <v>4670.4000000000005</v>
+      </c>
+      <c r="L13" s="15">
+        <f>I12+L12</f>
+        <v>27.200000000000003</v>
+      </c>
+      <c r="Q13"/>
+      <c r="R13"/>
+      <c r="S13"/>
+      <c r="T13"/>
+      <c r="U13"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="2"/>
